--- a/data/trans_camb/IP1008-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Edad-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,94</t>
+          <t>-2,3; 0,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,0</t>
+          <t>-2,91; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,9</t>
+          <t>-0,71; 0,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,0</t>
+          <t>-1,34; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,71</t>
+          <t>-0,39; 1,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,66</t>
+          <t>-0,42; 1,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,0</t>
+          <t>-1,75; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,5</t>
+          <t>-0,75; 0,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,47</t>
+          <t>-0,76; 0,46</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,29</t>
+          <t>-0,78; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,74</t>
+          <t>-0,42; 2,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,0</t>
+          <t>-3,25; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,0</t>
+          <t>-2,89; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,64</t>
+          <t>-1,33; 0,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,93</t>
+          <t>-1,2; 0,96</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; -0,33</t>
+          <t>-2,89; -0,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,57</t>
+          <t>-1,36; 2,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,53</t>
+          <t>-0,3; 2,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,11</t>
+          <t>-0,87; 0,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,92</t>
+          <t>-0,39; 1,89</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-84,55; 566,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,26; 753,9</t>
+          <t>-52,95; 909,12</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,67</t>
+          <t>-0,5; 0,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,22</t>
+          <t>-0,26; 1,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,41</t>
+          <t>-0,77; 0,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,15</t>
+          <t>-0,87; 0,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,34</t>
+          <t>-0,51; 0,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,5</t>
+          <t>-0,39; 0,48</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-77,98; 372,18</t>
+          <t>-77,53; 524,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 698,16</t>
+          <t>-46,36; 667,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,72; 188,45</t>
+          <t>-81,62; 184,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,21</t>
+          <t>-100,0; 94,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-62,78; 108,17</t>
+          <t>-65,25; 123,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-56,52; 167,65</t>
+          <t>-55,52; 164,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1008-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Edad-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,0</t>
+          <t>-3,34; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,9</t>
+          <t>-0,8; 1,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,0</t>
+          <t>-1,4; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,85</t>
+          <t>-0,26; 1,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,95</t>
+          <t>-0,43; 1,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,0</t>
+          <t>-1,62; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,0</t>
+          <t>-1,89; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,5</t>
+          <t>-0,66; 0,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,46</t>
+          <t>-0,66; 0,47</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,31</t>
+          <t>-0,78; 2,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,89</t>
+          <t>-0,82; 2,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,0</t>
+          <t>-3,12; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,0</t>
+          <t>-2,95; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,65</t>
+          <t>-1,4; 0,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,96</t>
+          <t>-1,26; 0,94</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; -0,34</t>
+          <t>-2,84; -0,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,66</t>
+          <t>-1,37; 2,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,01; 3,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,61</t>
+          <t>-0,33; 2,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,98</t>
+          <t>-0,97; 1,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,89</t>
+          <t>-0,48; 1,82</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 569,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,95; 909,12</t>
+          <t>-54,75; 786,28</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,68</t>
+          <t>-0,55; 0,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,15</t>
+          <t>-0,22; 1,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,41</t>
+          <t>-0,76; 0,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,15</t>
+          <t>-0,96; 0,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,35</t>
+          <t>-0,45; 0,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,48</t>
+          <t>-0,38; 0,49</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-77,53; 524,61</t>
+          <t>-76,44; 451,27</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,36; 667,12</t>
+          <t>-39,9; 705,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,62; 184,4</t>
+          <t>-80,98; 224,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 94,32</t>
+          <t>-100,0; 156,29</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,25; 123,68</t>
+          <t>-63,35; 109,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,52; 164,95</t>
+          <t>-55,78; 188,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1008-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1008-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,58</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>-2,34; 0,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,21; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,94</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,02</t>
+          <t>-0,84; 0,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,0</t>
+          <t>-1,56; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-19,68%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-19,68%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,54</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,4</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,64</t>
+          <t>-1,87; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,72</t>
+          <t>-1,89; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,0</t>
+          <t>-0,26; 1,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,0</t>
+          <t>-0,36; 1,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,61</t>
+          <t>-0,65; 0,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,47</t>
+          <t>-0,65; 0,47</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>149,08%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>157,72%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,96</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,96</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,48</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,81</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,32</t>
+          <t>-3,08; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,56</t>
+          <t>-3,62; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,0</t>
+          <t>-0,77; 2,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,0</t>
+          <t>-0,57; 2,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,66</t>
+          <t>-1,3; 0,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,94</t>
+          <t>-1,43; 0,93</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>117,42%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>196,46%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,79</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-1,06</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,41</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,13</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; -0,34</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,27</t>
+          <t>-0,33; 2,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,29</t>
+          <t>-2,93; -0,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,74</t>
+          <t>-1,4; 2,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,11</t>
+          <t>-0,86; 1,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,82</t>
+          <t>-0,45; 1,92</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>341,81%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>239,51%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>39,01%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>341,81%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>239,51%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 569,76</t>
+          <t>-84,55; 566,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,75; 786,28</t>
+          <t>-53,26; 753,9</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,02</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,41</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,69</t>
+          <t>-0,78; 0,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 1,24</t>
+          <t>-0,95; 0,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,42</t>
+          <t>-0,57; 0,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,19</t>
+          <t>-0,27; 1,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,32</t>
+          <t>-0,49; 0,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,49</t>
+          <t>-0,39; 0,5</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-23,05%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-53,89%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>4,63%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>87,18%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-23,05%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-53,89%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-76,44; 451,27</t>
+          <t>-80,72; 188,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 705,62</t>
+          <t>-100,0; 121,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,98; 224,47</t>
+          <t>-77,98; 372,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 156,29</t>
+          <t>-46,07; 698,16</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-63,35; 109,5</t>
+          <t>-62,78; 108,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,78; 188,55</t>
+          <t>-56,52; 167,65</t>
         </is>
       </c>
     </row>
